--- a/docs/legal-acts/export/SK 2020-78.xlsx
+++ b/docs/legal-acts/export/SK 2020-78.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 18:24</t>
+          <t>2026-10-21 18:31</t>
         </is>
       </c>
     </row>
@@ -18919,7 +18919,7 @@
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr">
@@ -19008,7 +19008,7 @@
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G192" s="3" t="inlineStr">
@@ -19097,7 +19097,7 @@
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G193" s="3" t="inlineStr">
@@ -19186,7 +19186,7 @@
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr">
@@ -19275,7 +19275,7 @@
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr">
@@ -19364,7 +19364,7 @@
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr">
@@ -19453,7 +19453,7 @@
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
@@ -19542,7 +19542,7 @@
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
@@ -19631,7 +19631,7 @@
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr">
@@ -19720,7 +19720,7 @@
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G200" s="3" t="inlineStr">
@@ -19809,7 +19809,7 @@
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr">
@@ -19898,7 +19898,7 @@
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr">
@@ -19987,7 +19987,7 @@
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G203" s="3" t="inlineStr">
@@ -20076,7 +20076,7 @@
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr">
@@ -20165,7 +20165,7 @@
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr">
@@ -20254,7 +20254,7 @@
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr">
@@ -20343,7 +20343,7 @@
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G207" s="3" t="inlineStr">
@@ -20432,7 +20432,7 @@
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G208" s="3" t="inlineStr">
@@ -20521,7 +20521,7 @@
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G209" s="3" t="inlineStr">
@@ -20610,7 +20610,7 @@
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
@@ -20699,7 +20699,7 @@
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
@@ -20788,7 +20788,7 @@
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr">
@@ -20877,7 +20877,7 @@
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr">
@@ -20966,7 +20966,7 @@
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr">
@@ -21055,7 +21055,7 @@
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G215" s="3" t="inlineStr">
@@ -21144,7 +21144,7 @@
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr">
@@ -21233,7 +21233,7 @@
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G217" s="3" t="inlineStr">
@@ -21322,7 +21322,7 @@
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G218" s="3" t="inlineStr">
@@ -21411,7 +21411,7 @@
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G219" s="3" t="inlineStr">
@@ -21500,7 +21500,7 @@
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr">
@@ -21589,7 +21589,7 @@
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
@@ -21678,7 +21678,7 @@
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G222" s="3" t="inlineStr">
@@ -21767,7 +21767,7 @@
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G223" s="3" t="inlineStr">
@@ -21856,7 +21856,7 @@
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr">
@@ -21945,7 +21945,7 @@
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G225" s="3" t="inlineStr">
@@ -22034,7 +22034,7 @@
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr">
@@ -22123,7 +22123,7 @@
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
@@ -22212,7 +22212,7 @@
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G228" s="3" t="inlineStr">
@@ -22301,7 +22301,7 @@
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
@@ -22390,7 +22390,7 @@
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr">
@@ -22479,7 +22479,7 @@
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
@@ -22568,7 +22568,7 @@
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G232" s="3" t="inlineStr">
@@ -22657,7 +22657,7 @@
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
@@ -22746,7 +22746,7 @@
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
@@ -22835,7 +22835,7 @@
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
@@ -22924,7 +22924,7 @@
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr">
@@ -23013,7 +23013,7 @@
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G237" s="3" t="inlineStr">
@@ -23102,7 +23102,7 @@
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
@@ -23191,7 +23191,7 @@
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
@@ -23280,7 +23280,7 @@
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
@@ -23369,7 +23369,7 @@
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G241" s="3" t="inlineStr">
@@ -23458,7 +23458,7 @@
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G242" s="3" t="inlineStr">
@@ -23547,7 +23547,7 @@
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G243" s="3" t="inlineStr">
@@ -23636,7 +23636,7 @@
       </c>
       <c r="F244" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G244" s="3" t="inlineStr">
@@ -23725,7 +23725,7 @@
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G245" s="3" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G246" s="3" t="inlineStr">
@@ -23903,7 +23903,7 @@
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G247" s="3" t="inlineStr">
@@ -23992,7 +23992,7 @@
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G248" s="3" t="inlineStr">
@@ -24081,7 +24081,7 @@
       </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G249" s="3" t="inlineStr">
@@ -24170,7 +24170,7 @@
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G250" s="3" t="inlineStr">
@@ -24259,7 +24259,7 @@
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
@@ -24348,7 +24348,7 @@
       </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G252" s="3" t="inlineStr">
@@ -24437,7 +24437,7 @@
       </c>
       <c r="F253" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G253" s="3" t="inlineStr">
@@ -24526,7 +24526,7 @@
       </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G254" s="3" t="inlineStr">
@@ -24615,7 +24615,7 @@
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G255" s="3" t="inlineStr">
@@ -24704,7 +24704,7 @@
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G256" s="3" t="inlineStr">
@@ -24793,7 +24793,7 @@
       </c>
       <c r="F257" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G257" s="3" t="inlineStr">
@@ -24882,7 +24882,7 @@
       </c>
       <c r="F258" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G258" s="3" t="inlineStr">
@@ -24971,7 +24971,7 @@
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G259" s="3" t="inlineStr">
@@ -25060,7 +25060,7 @@
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
@@ -25149,7 +25149,7 @@
       </c>
       <c r="F261" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G261" s="3" t="inlineStr">
@@ -25238,7 +25238,7 @@
       </c>
       <c r="F262" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G262" s="3" t="inlineStr">
@@ -25327,7 +25327,7 @@
       </c>
       <c r="F263" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G263" s="3" t="inlineStr">
@@ -25416,7 +25416,7 @@
       </c>
       <c r="F264" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G264" s="3" t="inlineStr">
@@ -25505,7 +25505,7 @@
       </c>
       <c r="F265" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G265" s="3" t="inlineStr">
@@ -25594,7 +25594,7 @@
       </c>
       <c r="F266" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G266" s="3" t="inlineStr">
@@ -25683,7 +25683,7 @@
       </c>
       <c r="F267" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G267" s="3" t="inlineStr">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="F268" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G268" s="3" t="inlineStr">
@@ -25861,7 +25861,7 @@
       </c>
       <c r="F269" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G269" s="3" t="inlineStr">
@@ -25950,7 +25950,7 @@
       </c>
       <c r="F270" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G270" s="3" t="inlineStr">
@@ -26039,7 +26039,7 @@
       </c>
       <c r="F271" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G271" s="3" t="inlineStr">
@@ -26128,7 +26128,7 @@
       </c>
       <c r="F272" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G272" s="3" t="inlineStr">
@@ -26217,7 +26217,7 @@
       </c>
       <c r="F273" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G273" s="3" t="inlineStr">
@@ -26306,7 +26306,7 @@
       </c>
       <c r="F274" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G274" s="3" t="inlineStr">
@@ -26395,7 +26395,7 @@
       </c>
       <c r="F275" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G275" s="3" t="inlineStr">
@@ -26484,7 +26484,7 @@
       </c>
       <c r="F276" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G276" s="3" t="inlineStr">
@@ -26573,7 +26573,7 @@
       </c>
       <c r="F277" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G277" s="3" t="inlineStr">
@@ -26662,7 +26662,7 @@
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr">
@@ -26751,7 +26751,7 @@
       </c>
       <c r="F279" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
@@ -26840,7 +26840,7 @@
       </c>
       <c r="F280" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
@@ -26929,7 +26929,7 @@
       </c>
       <c r="F281" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G281" s="3" t="inlineStr">
@@ -27018,7 +27018,7 @@
       </c>
       <c r="F282" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G282" s="3" t="inlineStr">
@@ -27107,7 +27107,7 @@
       </c>
       <c r="F283" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G283" s="3" t="inlineStr">
@@ -27196,7 +27196,7 @@
       </c>
       <c r="F284" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G284" s="3" t="inlineStr">
@@ -27285,7 +27285,7 @@
       </c>
       <c r="F285" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G285" s="3" t="inlineStr">
@@ -27374,7 +27374,7 @@
       </c>
       <c r="F286" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G286" s="3" t="inlineStr">
@@ -27463,7 +27463,7 @@
       </c>
       <c r="F287" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
@@ -27552,7 +27552,7 @@
       </c>
       <c r="F288" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G288" s="3" t="inlineStr">
@@ -27641,7 +27641,7 @@
       </c>
       <c r="F289" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G289" s="3" t="inlineStr">
@@ -27730,7 +27730,7 @@
       </c>
       <c r="F290" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
@@ -27819,7 +27819,7 @@
       </c>
       <c r="F291" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G291" s="3" t="inlineStr">
@@ -27908,7 +27908,7 @@
       </c>
       <c r="F292" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G292" s="3" t="inlineStr">
@@ -27997,7 +27997,7 @@
       </c>
       <c r="F293" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G293" s="3" t="inlineStr">
@@ -28086,7 +28086,7 @@
       </c>
       <c r="F294" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G294" s="3" t="inlineStr">
@@ -28175,7 +28175,7 @@
       </c>
       <c r="F295" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G295" s="3" t="inlineStr">
@@ -28264,7 +28264,7 @@
       </c>
       <c r="F296" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G296" s="3" t="inlineStr">
@@ -28353,7 +28353,7 @@
       </c>
       <c r="F297" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G297" s="3" t="inlineStr">
@@ -28442,7 +28442,7 @@
       </c>
       <c r="F298" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G298" s="3" t="inlineStr">
@@ -28531,7 +28531,7 @@
       </c>
       <c r="F299" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G299" s="3" t="inlineStr">
@@ -28620,7 +28620,7 @@
       </c>
       <c r="F300" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G300" s="3" t="inlineStr">
@@ -28709,7 +28709,7 @@
       </c>
       <c r="F301" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G301" s="3" t="inlineStr">
@@ -28798,7 +28798,7 @@
       </c>
       <c r="F302" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G302" s="3" t="inlineStr">
@@ -28887,7 +28887,7 @@
       </c>
       <c r="F303" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G303" s="3" t="inlineStr">
@@ -28976,7 +28976,7 @@
       </c>
       <c r="F304" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G304" s="3" t="inlineStr">
@@ -29065,7 +29065,7 @@
       </c>
       <c r="F305" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G305" s="3" t="inlineStr">
@@ -29154,7 +29154,7 @@
       </c>
       <c r="F306" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G306" s="3" t="inlineStr">
@@ -29243,7 +29243,7 @@
       </c>
       <c r="F307" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G307" s="3" t="inlineStr">
@@ -29332,7 +29332,7 @@
       </c>
       <c r="F308" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G308" s="3" t="inlineStr">
@@ -29421,7 +29421,7 @@
       </c>
       <c r="F309" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G309" s="3" t="inlineStr">
@@ -29510,7 +29510,7 @@
       </c>
       <c r="F310" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G310" s="3" t="inlineStr">
@@ -29599,7 +29599,7 @@
       </c>
       <c r="F311" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G311" s="3" t="inlineStr">
@@ -29688,7 +29688,7 @@
       </c>
       <c r="F312" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G312" s="3" t="inlineStr">
@@ -29777,7 +29777,7 @@
       </c>
       <c r="F313" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G313" s="3" t="inlineStr">
@@ -29866,7 +29866,7 @@
       </c>
       <c r="F314" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G314" s="3" t="inlineStr">
@@ -29955,7 +29955,7 @@
       </c>
       <c r="F315" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G315" s="3" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="F316" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G316" s="3" t="inlineStr">
@@ -30133,7 +30133,7 @@
       </c>
       <c r="F317" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G317" s="3" t="inlineStr">
@@ -30222,7 +30222,7 @@
       </c>
       <c r="F318" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G318" s="3" t="inlineStr">
@@ -30311,7 +30311,7 @@
       </c>
       <c r="F319" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G319" s="3" t="inlineStr">
@@ -30400,7 +30400,7 @@
       </c>
       <c r="F320" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G320" s="3" t="inlineStr">
@@ -30489,7 +30489,7 @@
       </c>
       <c r="F321" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G321" s="3" t="inlineStr">
@@ -30578,7 +30578,7 @@
       </c>
       <c r="F322" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G322" s="3" t="inlineStr">
@@ -30667,7 +30667,7 @@
       </c>
       <c r="F323" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G323" s="3" t="inlineStr">
@@ -30756,7 +30756,7 @@
       </c>
       <c r="F324" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G324" s="3" t="inlineStr">
@@ -30845,7 +30845,7 @@
       </c>
       <c r="F325" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G325" s="3" t="inlineStr">
@@ -30934,7 +30934,7 @@
       </c>
       <c r="F326" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G326" s="3" t="inlineStr">
@@ -31023,7 +31023,7 @@
       </c>
       <c r="F327" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G327" s="3" t="inlineStr">
@@ -31112,7 +31112,7 @@
       </c>
       <c r="F328" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G328" s="3" t="inlineStr">
@@ -31201,7 +31201,7 @@
       </c>
       <c r="F329" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G329" s="3" t="inlineStr">
@@ -31290,7 +31290,7 @@
       </c>
       <c r="F330" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G330" s="3" t="inlineStr">
@@ -31379,7 +31379,7 @@
       </c>
       <c r="F331" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G331" s="3" t="inlineStr">
@@ -31468,7 +31468,7 @@
       </c>
       <c r="F332" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G332" s="3" t="inlineStr">
@@ -31557,7 +31557,7 @@
       </c>
       <c r="F333" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G333" s="3" t="inlineStr">
@@ -31646,7 +31646,7 @@
       </c>
       <c r="F334" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G334" s="3" t="inlineStr">
@@ -31735,7 +31735,7 @@
       </c>
       <c r="F335" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G335" s="3" t="inlineStr">
@@ -31824,7 +31824,7 @@
       </c>
       <c r="F336" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G336" s="3" t="inlineStr">
@@ -31913,7 +31913,7 @@
       </c>
       <c r="F337" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G337" s="3" t="inlineStr">
@@ -32002,7 +32002,7 @@
       </c>
       <c r="F338" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G338" s="3" t="inlineStr">
@@ -32091,7 +32091,7 @@
       </c>
       <c r="F339" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G339" s="3" t="inlineStr">
@@ -32180,7 +32180,7 @@
       </c>
       <c r="F340" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G340" s="3" t="inlineStr">
@@ -32269,7 +32269,7 @@
       </c>
       <c r="F341" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G341" s="3" t="inlineStr">
@@ -32358,7 +32358,7 @@
       </c>
       <c r="F342" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G342" s="3" t="inlineStr">
@@ -32447,7 +32447,7 @@
       </c>
       <c r="F343" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G343" s="3" t="inlineStr">
@@ -32536,7 +32536,7 @@
       </c>
       <c r="F344" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G344" s="3" t="inlineStr">
@@ -32625,7 +32625,7 @@
       </c>
       <c r="F345" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G345" s="3" t="inlineStr">
@@ -32714,7 +32714,7 @@
       </c>
       <c r="F346" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G346" s="3" t="inlineStr">
@@ -32803,7 +32803,7 @@
       </c>
       <c r="F347" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G347" s="3" t="inlineStr">
@@ -32892,7 +32892,7 @@
       </c>
       <c r="F348" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G348" s="3" t="inlineStr">
@@ -32981,7 +32981,7 @@
       </c>
       <c r="F349" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G349" s="3" t="inlineStr">
@@ -33070,7 +33070,7 @@
       </c>
       <c r="F350" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G350" s="3" t="inlineStr">
@@ -33159,7 +33159,7 @@
       </c>
       <c r="F351" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G351" s="3" t="inlineStr">
@@ -33248,7 +33248,7 @@
       </c>
       <c r="F352" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G352" s="3" t="inlineStr">
@@ -33337,7 +33337,7 @@
       </c>
       <c r="F353" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G353" s="3" t="inlineStr">
@@ -33426,7 +33426,7 @@
       </c>
       <c r="F354" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G354" s="3" t="inlineStr">
@@ -33515,7 +33515,7 @@
       </c>
       <c r="F355" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G355" s="3" t="inlineStr">
@@ -33604,7 +33604,7 @@
       </c>
       <c r="F356" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G356" s="3" t="inlineStr">
@@ -33693,7 +33693,7 @@
       </c>
       <c r="F357" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G357" s="3" t="inlineStr">
@@ -33782,7 +33782,7 @@
       </c>
       <c r="F358" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G358" s="3" t="inlineStr">
@@ -33871,7 +33871,7 @@
       </c>
       <c r="F359" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G359" s="3" t="inlineStr">
@@ -33960,7 +33960,7 @@
       </c>
       <c r="F360" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G360" s="3" t="inlineStr">
@@ -34049,7 +34049,7 @@
       </c>
       <c r="F361" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G361" s="3" t="inlineStr">
@@ -34138,7 +34138,7 @@
       </c>
       <c r="F362" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G362" s="3" t="inlineStr">
@@ -34227,7 +34227,7 @@
       </c>
       <c r="F363" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G363" s="3" t="inlineStr">
@@ -34316,7 +34316,7 @@
       </c>
       <c r="F364" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G364" s="3" t="inlineStr">
@@ -34405,7 +34405,7 @@
       </c>
       <c r="F365" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G365" s="3" t="inlineStr">
@@ -34494,7 +34494,7 @@
       </c>
       <c r="F366" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G366" s="3" t="inlineStr">
@@ -34583,7 +34583,7 @@
       </c>
       <c r="F367" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G367" s="3" t="inlineStr">
@@ -34672,7 +34672,7 @@
       </c>
       <c r="F368" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G368" s="3" t="inlineStr">
@@ -34761,7 +34761,7 @@
       </c>
       <c r="F369" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G369" s="3" t="inlineStr">
@@ -34850,7 +34850,7 @@
       </c>
       <c r="F370" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G370" s="3" t="inlineStr">
@@ -34939,7 +34939,7 @@
       </c>
       <c r="F371" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G371" s="3" t="inlineStr">
@@ -35028,7 +35028,7 @@
       </c>
       <c r="F372" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G372" s="3" t="inlineStr">
@@ -35117,7 +35117,7 @@
       </c>
       <c r="F373" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G373" s="3" t="inlineStr">
@@ -35206,7 +35206,7 @@
       </c>
       <c r="F374" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G374" s="3" t="inlineStr">
@@ -35295,7 +35295,7 @@
       </c>
       <c r="F375" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G375" s="3" t="inlineStr">
@@ -35384,7 +35384,7 @@
       </c>
       <c r="F376" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G376" s="3" t="inlineStr">
@@ -35473,7 +35473,7 @@
       </c>
       <c r="F377" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G377" s="3" t="inlineStr">
@@ -35562,7 +35562,7 @@
       </c>
       <c r="F378" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G378" s="3" t="inlineStr">
@@ -35651,7 +35651,7 @@
       </c>
       <c r="F379" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G379" s="3" t="inlineStr">
@@ -35740,7 +35740,7 @@
       </c>
       <c r="F380" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G380" s="3" t="inlineStr">
@@ -35829,7 +35829,7 @@
       </c>
       <c r="F381" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G381" s="3" t="inlineStr">
@@ -35918,7 +35918,7 @@
       </c>
       <c r="F382" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G382" s="3" t="inlineStr">
@@ -36007,7 +36007,7 @@
       </c>
       <c r="F383" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G383" s="3" t="inlineStr">
@@ -36096,7 +36096,7 @@
       </c>
       <c r="F384" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G384" s="3" t="inlineStr">
@@ -36185,7 +36185,7 @@
       </c>
       <c r="F385" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G385" s="3" t="inlineStr">
@@ -36274,7 +36274,7 @@
       </c>
       <c r="F386" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G386" s="3" t="inlineStr">
@@ -36363,7 +36363,7 @@
       </c>
       <c r="F387" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G387" s="3" t="inlineStr">
@@ -36452,7 +36452,7 @@
       </c>
       <c r="F388" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G388" s="3" t="inlineStr">
@@ -36541,7 +36541,7 @@
       </c>
       <c r="F389" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G389" s="3" t="inlineStr">
@@ -36630,7 +36630,7 @@
       </c>
       <c r="F390" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G390" s="3" t="inlineStr">
@@ -36719,7 +36719,7 @@
       </c>
       <c r="F391" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G391" s="3" t="inlineStr">
@@ -36808,7 +36808,7 @@
       </c>
       <c r="F392" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G392" s="3" t="inlineStr">
@@ -36897,7 +36897,7 @@
       </c>
       <c r="F393" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G393" s="3" t="inlineStr">
@@ -36986,7 +36986,7 @@
       </c>
       <c r="F394" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G394" s="3" t="inlineStr">
@@ -37075,7 +37075,7 @@
       </c>
       <c r="F395" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G395" s="3" t="inlineStr">
@@ -37164,7 +37164,7 @@
       </c>
       <c r="F396" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G396" s="3" t="inlineStr">
@@ -37253,7 +37253,7 @@
       </c>
       <c r="F397" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G397" s="3" t="inlineStr">
@@ -37342,7 +37342,7 @@
       </c>
       <c r="F398" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G398" s="3" t="inlineStr">
@@ -37431,7 +37431,7 @@
       </c>
       <c r="F399" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G399" s="3" t="inlineStr">
@@ -37520,7 +37520,7 @@
       </c>
       <c r="F400" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G400" s="3" t="inlineStr">
@@ -37609,7 +37609,7 @@
       </c>
       <c r="F401" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G401" s="3" t="inlineStr">
@@ -37698,7 +37698,7 @@
       </c>
       <c r="F402" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G402" s="3" t="inlineStr">
@@ -37787,7 +37787,7 @@
       </c>
       <c r="F403" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G403" s="3" t="inlineStr">
@@ -37876,7 +37876,7 @@
       </c>
       <c r="F404" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G404" s="3" t="inlineStr">
@@ -37965,7 +37965,7 @@
       </c>
       <c r="F405" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G405" s="3" t="inlineStr">
@@ -38054,7 +38054,7 @@
       </c>
       <c r="F406" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G406" s="3" t="inlineStr">
@@ -38143,7 +38143,7 @@
       </c>
       <c r="F407" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G407" s="3" t="inlineStr">
@@ -38232,7 +38232,7 @@
       </c>
       <c r="F408" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G408" s="3" t="inlineStr">
@@ -38321,7 +38321,7 @@
       </c>
       <c r="F409" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G409" s="3" t="inlineStr">
@@ -38410,7 +38410,7 @@
       </c>
       <c r="F410" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G410" s="3" t="inlineStr">
@@ -38499,7 +38499,7 @@
       </c>
       <c r="F411" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G411" s="3" t="inlineStr">
@@ -38588,7 +38588,7 @@
       </c>
       <c r="F412" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G412" s="3" t="inlineStr">
@@ -38677,7 +38677,7 @@
       </c>
       <c r="F413" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G413" s="3" t="inlineStr">
@@ -38766,7 +38766,7 @@
       </c>
       <c r="F414" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G414" s="3" t="inlineStr">
@@ -38855,7 +38855,7 @@
       </c>
       <c r="F415" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G415" s="3" t="inlineStr">
@@ -38944,7 +38944,7 @@
       </c>
       <c r="F416" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G416" s="3" t="inlineStr">
@@ -39033,7 +39033,7 @@
       </c>
       <c r="F417" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G417" s="3" t="inlineStr">
@@ -39122,7 +39122,7 @@
       </c>
       <c r="F418" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G418" s="3" t="inlineStr">
@@ -39211,7 +39211,7 @@
       </c>
       <c r="F419" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G419" s="3" t="inlineStr">
@@ -39300,7 +39300,7 @@
       </c>
       <c r="F420" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G420" s="3" t="inlineStr">
@@ -39389,7 +39389,7 @@
       </c>
       <c r="F421" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G421" s="3" t="inlineStr">
@@ -39478,7 +39478,7 @@
       </c>
       <c r="F422" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G422" s="3" t="inlineStr">
@@ -39567,7 +39567,7 @@
       </c>
       <c r="F423" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G423" s="3" t="inlineStr">
@@ -39656,7 +39656,7 @@
       </c>
       <c r="F424" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G424" s="3" t="inlineStr">
@@ -39745,7 +39745,7 @@
       </c>
       <c r="F425" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G425" s="3" t="inlineStr">
@@ -39834,7 +39834,7 @@
       </c>
       <c r="F426" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G426" s="3" t="inlineStr">
@@ -39923,7 +39923,7 @@
       </c>
       <c r="F427" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G427" s="3" t="inlineStr">
@@ -40012,7 +40012,7 @@
       </c>
       <c r="F428" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G428" s="3" t="inlineStr">
@@ -40101,7 +40101,7 @@
       </c>
       <c r="F429" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G429" s="3" t="inlineStr">
@@ -40190,7 +40190,7 @@
       </c>
       <c r="F430" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G430" s="3" t="inlineStr">
@@ -40279,7 +40279,7 @@
       </c>
       <c r="F431" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G431" s="3" t="inlineStr">
@@ -40368,7 +40368,7 @@
       </c>
       <c r="F432" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G432" s="3" t="inlineStr">
@@ -40457,7 +40457,7 @@
       </c>
       <c r="F433" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G433" s="3" t="inlineStr">
@@ -40546,7 +40546,7 @@
       </c>
       <c r="F434" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G434" s="3" t="inlineStr">
@@ -40635,7 +40635,7 @@
       </c>
       <c r="F435" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G435" s="3" t="inlineStr">
@@ -40724,7 +40724,7 @@
       </c>
       <c r="F436" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G436" s="3" t="inlineStr">
@@ -40813,7 +40813,7 @@
       </c>
       <c r="F437" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G437" s="3" t="inlineStr">
@@ -40902,7 +40902,7 @@
       </c>
       <c r="F438" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G438" s="3" t="inlineStr">
@@ -40991,7 +40991,7 @@
       </c>
       <c r="F439" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G439" s="3" t="inlineStr">
@@ -41080,7 +41080,7 @@
       </c>
       <c r="F440" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G440" s="3" t="inlineStr">
@@ -41169,7 +41169,7 @@
       </c>
       <c r="F441" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G441" s="3" t="inlineStr">
@@ -41258,7 +41258,7 @@
       </c>
       <c r="F442" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G442" s="3" t="inlineStr"/>
@@ -41343,7 +41343,7 @@
       </c>
       <c r="F443" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G443" s="3" t="inlineStr"/>
@@ -41428,7 +41428,7 @@
       </c>
       <c r="F444" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G444" s="3" t="inlineStr"/>
@@ -41513,7 +41513,7 @@
       </c>
       <c r="F445" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G445" s="3" t="inlineStr"/>
@@ -41598,7 +41598,7 @@
       </c>
       <c r="F446" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G446" s="3" t="inlineStr"/>
@@ -41683,7 +41683,7 @@
       </c>
       <c r="F447" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G447" s="3" t="inlineStr"/>
@@ -41768,7 +41768,7 @@
       </c>
       <c r="F448" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G448" s="3" t="inlineStr"/>
@@ -41853,7 +41853,7 @@
       </c>
       <c r="F449" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G449" s="3" t="inlineStr"/>
@@ -41938,7 +41938,7 @@
       </c>
       <c r="F450" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G450" s="3" t="inlineStr"/>
@@ -42023,7 +42023,7 @@
       </c>
       <c r="F451" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G451" s="3" t="inlineStr"/>
@@ -42108,7 +42108,7 @@
       </c>
       <c r="F452" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G452" s="3" t="inlineStr"/>
@@ -42193,7 +42193,7 @@
       </c>
       <c r="F453" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G453" s="3" t="inlineStr"/>
@@ -42278,7 +42278,7 @@
       </c>
       <c r="F454" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G454" s="3" t="inlineStr"/>
@@ -42363,7 +42363,7 @@
       </c>
       <c r="F455" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G455" s="3" t="inlineStr"/>
@@ -44645,7 +44645,7 @@
       </c>
       <c r="F481" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G481" s="3" t="inlineStr"/>
@@ -44730,7 +44730,7 @@
       </c>
       <c r="F482" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G482" s="3" t="inlineStr"/>
@@ -44815,7 +44815,7 @@
       </c>
       <c r="F483" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G483" s="3" t="inlineStr"/>
@@ -44900,7 +44900,7 @@
       </c>
       <c r="F484" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G484" s="3" t="inlineStr"/>
@@ -44985,7 +44985,7 @@
       </c>
       <c r="F485" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G485" s="3" t="inlineStr"/>
@@ -45070,7 +45070,7 @@
       </c>
       <c r="F486" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G486" s="3" t="inlineStr"/>
@@ -45155,7 +45155,7 @@
       </c>
       <c r="F487" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G487" s="3" t="inlineStr"/>
@@ -45325,7 +45325,7 @@
       </c>
       <c r="F489" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G489" s="3" t="inlineStr"/>
@@ -45410,7 +45410,7 @@
       </c>
       <c r="F490" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G490" s="3" t="inlineStr"/>
@@ -45495,7 +45495,7 @@
       </c>
       <c r="F491" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G491" s="3" t="inlineStr"/>
@@ -45580,7 +45580,7 @@
       </c>
       <c r="F492" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G492" s="3" t="inlineStr"/>
@@ -45665,7 +45665,7 @@
       </c>
       <c r="F493" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G493" s="3" t="inlineStr"/>
@@ -45750,7 +45750,7 @@
       </c>
       <c r="F494" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G494" s="3" t="inlineStr"/>
@@ -45835,7 +45835,7 @@
       </c>
       <c r="F495" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G495" s="3" t="inlineStr"/>
@@ -45920,7 +45920,7 @@
       </c>
       <c r="F496" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G496" s="3" t="inlineStr"/>
@@ -46005,7 +46005,7 @@
       </c>
       <c r="F497" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G497" s="3" t="inlineStr"/>
@@ -46090,7 +46090,7 @@
       </c>
       <c r="F498" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G498" s="3" t="inlineStr"/>
@@ -46175,7 +46175,7 @@
       </c>
       <c r="F499" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G499" s="3" t="inlineStr"/>
@@ -46260,7 +46260,7 @@
       </c>
       <c r="F500" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G500" s="3" t="inlineStr"/>
@@ -46345,7 +46345,7 @@
       </c>
       <c r="F501" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G501" s="3" t="inlineStr"/>
@@ -46430,7 +46430,7 @@
       </c>
       <c r="F502" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G502" s="3" t="inlineStr"/>
@@ -46515,7 +46515,7 @@
       </c>
       <c r="F503" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G503" s="3" t="inlineStr"/>
@@ -46600,7 +46600,7 @@
       </c>
       <c r="F504" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="G504" s="3" t="inlineStr"/>
